--- a/Results_isofys/Andrea_bulk CN_2025.xlsx
+++ b/Results_isofys/Andrea_bulk CN_2025.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe.sharepoint.com/teams/BW24_TMP00528/Gedeelde documenten/General/DATA/EA/Andrea Chavez/Bulk plant samples - 2025/Resultaten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\NUMEX_preliminar\Results_isofys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="8_{2322B050-C2E9-406E-9395-63A10818E01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3020AF31-14E8-4AB5-9F17-14FCEE3FBB15}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{465A843A-9C4A-4A54-901A-09BDFDF6C3C9}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6420" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="number of samples" sheetId="7" r:id="rId1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="313">
   <si>
     <t>certified values</t>
   </si>
@@ -987,8 +986,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1164,7 +1163,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1499,18 +1498,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8876C304-4BCF-495F-8D21-2DE6C36CF9B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:D12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:4" ht="15">
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" ht="15">
       <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
@@ -1519,7 +1518,7 @@
       </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4" ht="15">
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
@@ -1527,7 +1526,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4" ht="15">
       <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
@@ -1535,7 +1534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4" ht="15">
       <c r="B7" s="6" t="s">
         <v>269</v>
       </c>
@@ -1543,7 +1542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4" ht="15">
       <c r="B8" s="6" t="s">
         <v>270</v>
       </c>
@@ -1551,7 +1550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:4" ht="15">
       <c r="B9" s="6" t="s">
         <v>271</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:4" ht="15">
       <c r="B10" s="6" t="s">
         <v>272</v>
       </c>
@@ -1567,7 +1566,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:4">
       <c r="C12">
         <f>SUM(C4:C10)</f>
         <v>379</v>
@@ -1580,21 +1579,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2679C6-3D14-45F2-B38C-10F95ABFA8BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" s="15" customFormat="1" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -1627,7 +1626,7 @@
       </c>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -1642,7 +1641,7 @@
       <c r="J3" s="18"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" s="8" customFormat="1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1674,7 +1673,7 @@
         <v>0.10743794455416091</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18">
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1685,7 +1684,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18">
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1696,7 +1695,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18">
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1707,7 +1706,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" s="6" customFormat="1" ht="15">
       <c r="A8"/>
       <c r="B8" s="7" t="s">
         <v>5</v>
@@ -1728,7 +1727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" s="6" customFormat="1" ht="15">
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1785,7 +1784,7 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="15">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1821,7 +1820,7 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="15">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1850,7 +1849,7 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1879,7 +1878,7 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="15">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1908,7 +1907,7 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1937,7 +1936,7 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="15">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1966,7 +1965,7 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="15">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1995,7 +1994,7 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -2024,7 +2023,7 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="15">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -2053,7 +2052,7 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="15">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -2082,7 +2081,7 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="15">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -2111,7 +2110,7 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -2140,7 +2139,7 @@
       <c r="Q22" s="5"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -2169,7 +2168,7 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="4"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -2198,7 +2197,7 @@
       <c r="Q24" s="5"/>
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2227,7 +2226,7 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="4"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2256,7 +2255,7 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="4"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="15">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -2285,7 +2284,7 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="4"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="15">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2314,7 +2313,7 @@
       <c r="Q28" s="5"/>
       <c r="R28" s="4"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="15">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -2343,7 +2342,7 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="4"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -2372,7 +2371,7 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="4"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -2401,7 +2400,7 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="4"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="15">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -2430,7 +2429,7 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="4"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" ht="15">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -2459,7 +2458,7 @@
       <c r="Q33" s="5"/>
       <c r="R33" s="4"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="15">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -2488,7 +2487,7 @@
       <c r="Q34" s="5"/>
       <c r="R34" s="4"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" ht="15">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -2517,7 +2516,7 @@
       <c r="Q35" s="5"/>
       <c r="R35" s="4"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="15">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -2546,7 +2545,7 @@
       <c r="Q36" s="5"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="15">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -2575,7 +2574,7 @@
       <c r="Q37" s="5"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" ht="15">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -2604,7 +2603,7 @@
       <c r="Q38" s="5"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="15">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -2633,7 +2632,7 @@
       <c r="Q39" s="5"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="15">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -2662,7 +2661,7 @@
       <c r="Q40" s="5"/>
       <c r="R40" s="4"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="15">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -2699,7 +2698,7 @@
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="15">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -2728,7 +2727,7 @@
       <c r="Q42" s="5"/>
       <c r="R42" s="4"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="15">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -2757,7 +2756,7 @@
       <c r="Q43" s="5"/>
       <c r="R43" s="4"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="15">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2786,7 +2785,7 @@
       <c r="Q44" s="5"/>
       <c r="R44" s="4"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="15">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -2815,7 +2814,7 @@
       <c r="Q45" s="5"/>
       <c r="R45" s="4"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" ht="15">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2844,7 +2843,7 @@
       <c r="Q46" s="5"/>
       <c r="R46" s="4"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="15">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -2873,7 +2872,7 @@
       <c r="Q47" s="5"/>
       <c r="R47" s="4"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" ht="15">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -2902,7 +2901,7 @@
       <c r="Q48" s="5"/>
       <c r="R48" s="4"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" ht="15">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -2931,7 +2930,7 @@
       <c r="Q49" s="5"/>
       <c r="R49" s="4"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="15">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -2968,7 +2967,7 @@
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" ht="15">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -2997,7 +2996,7 @@
       <c r="Q51" s="5"/>
       <c r="R51" s="4"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" ht="15">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -3026,7 +3025,7 @@
       <c r="Q52" s="5"/>
       <c r="R52" s="4"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="15">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -3055,7 +3054,7 @@
       <c r="Q53" s="5"/>
       <c r="R53" s="4"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" ht="15">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -3084,7 +3083,7 @@
       <c r="Q54" s="5"/>
       <c r="R54" s="4"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" ht="15">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -3113,7 +3112,7 @@
       <c r="Q55" s="5"/>
       <c r="R55" s="4"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" ht="15">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -3142,7 +3141,7 @@
       <c r="Q56" s="5"/>
       <c r="R56" s="4"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" ht="15">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -3171,7 +3170,7 @@
       <c r="Q57" s="5"/>
       <c r="R57" s="4"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" ht="15">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -3208,7 +3207,7 @@
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" ht="15">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -3237,7 +3236,7 @@
       <c r="Q59" s="5"/>
       <c r="R59" s="4"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" ht="15">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -3266,7 +3265,7 @@
       <c r="Q60" s="5"/>
       <c r="R60" s="4"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="15">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -3295,7 +3294,7 @@
       <c r="Q61" s="5"/>
       <c r="R61" s="4"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" ht="15">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -3324,7 +3323,7 @@
       <c r="Q62" s="5"/>
       <c r="R62" s="4"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" ht="15">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -3353,7 +3352,7 @@
       <c r="Q63" s="5"/>
       <c r="R63" s="4"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" ht="15">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -3382,7 +3381,7 @@
       <c r="Q64" s="5"/>
       <c r="R64" s="4"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" ht="15">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -3411,7 +3410,7 @@
       <c r="Q65" s="5"/>
       <c r="R65" s="4"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" ht="15">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -3440,7 +3439,7 @@
       <c r="Q66" s="5"/>
       <c r="R66" s="4"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" ht="15">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -3469,7 +3468,7 @@
       <c r="Q67" s="5"/>
       <c r="R67" s="4"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" ht="15">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -3498,7 +3497,7 @@
       <c r="Q68" s="5"/>
       <c r="R68" s="4"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" ht="15">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -3527,7 +3526,7 @@
       <c r="Q69" s="5"/>
       <c r="R69" s="4"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" ht="15">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -3564,7 +3563,7 @@
       <c r="Q70" s="5"/>
       <c r="R70" s="5"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="15">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -3593,7 +3592,7 @@
       <c r="Q71" s="5"/>
       <c r="R71" s="4"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" ht="15">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -3623,7 +3622,7 @@
       <c r="R72" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L10:T72">
+  <sortState ref="L10:T72">
     <sortCondition ref="L10:L72"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3632,20 +3631,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274DF7ED-5974-43B1-9666-6E301C3E4E25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M73"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" s="15" customFormat="1" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -3678,7 +3677,7 @@
       </c>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -3692,7 +3691,7 @@
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
     </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" s="8" customFormat="1">
       <c r="A4" s="8" t="s">
         <v>80</v>
       </c>
@@ -3725,7 +3724,7 @@
       </c>
       <c r="M4" s="9"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="B5" s="1"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -3736,7 +3735,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="7" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" s="6" customFormat="1" ht="15">
       <c r="A7"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
@@ -3757,7 +3756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" s="6" customFormat="1" ht="15">
       <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
@@ -3789,7 +3788,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -3816,7 +3815,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>80</v>
       </c>
@@ -3843,7 +3842,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>80</v>
       </c>
@@ -3870,7 +3869,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -3924,7 +3923,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -3978,7 +3977,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -4005,7 +4004,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -4032,7 +4031,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -4056,7 +4055,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>80</v>
       </c>
@@ -4080,7 +4079,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>80</v>
       </c>
@@ -4104,7 +4103,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -4128,7 +4127,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -4152,7 +4151,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -4176,7 +4175,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -4200,7 +4199,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -4224,7 +4223,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -4248,7 +4247,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -4272,7 +4271,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -4296,7 +4295,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4320,7 +4319,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -4344,7 +4343,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>80</v>
       </c>
@@ -4368,7 +4367,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -4392,7 +4391,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -4416,7 +4415,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -4440,7 +4439,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -4464,7 +4463,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -4488,7 +4487,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -4512,7 +4511,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -4536,7 +4535,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -4560,7 +4559,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -4584,7 +4583,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -4608,7 +4607,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -4632,7 +4631,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -4656,7 +4655,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -4680,7 +4679,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -4704,7 +4703,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>80</v>
       </c>
@@ -4728,7 +4727,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>80</v>
       </c>
@@ -4752,7 +4751,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>80</v>
       </c>
@@ -4776,7 +4775,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -4800,7 +4799,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>80</v>
       </c>
@@ -4824,7 +4823,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>80</v>
       </c>
@@ -4848,7 +4847,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -4896,7 +4895,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -4920,7 +4919,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -4944,7 +4943,7 @@
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>80</v>
       </c>
@@ -4968,7 +4967,7 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>80</v>
       </c>
@@ -4992,7 +4991,7 @@
       </c>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>80</v>
       </c>
@@ -5016,7 +5015,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>80</v>
       </c>
@@ -5040,7 +5039,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>80</v>
       </c>
@@ -5064,7 +5063,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>80</v>
       </c>
@@ -5088,7 +5087,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>80</v>
       </c>
@@ -5112,7 +5111,7 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -5136,7 +5135,7 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -5160,7 +5159,7 @@
       </c>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>80</v>
       </c>
@@ -5184,7 +5183,7 @@
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -5208,7 +5207,7 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -5232,7 +5231,7 @@
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -5256,7 +5255,7 @@
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>80</v>
       </c>
@@ -5280,7 +5279,7 @@
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -5304,7 +5303,7 @@
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -5328,7 +5327,7 @@
       </c>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -5352,7 +5351,7 @@
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -5383,22 +5382,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A397A1C-3030-4C42-9EA5-D28B8C805E76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="8.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" s="15" customFormat="1" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -5431,7 +5430,7 @@
       </c>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -5446,7 +5445,7 @@
       <c r="J3" s="18"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" s="8" customFormat="1">
       <c r="A4" s="8" t="s">
         <v>153</v>
       </c>
@@ -5479,14 +5478,14 @@
       </c>
       <c r="M4" s="9"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="B5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13">
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" s="6" customFormat="1" ht="15">
       <c r="A7"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
@@ -5507,7 +5506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" s="6" customFormat="1" ht="15">
       <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
@@ -5537,7 +5536,7 @@
       </c>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>153</v>
       </c>
@@ -5562,7 +5561,7 @@
       <c r="J9" s="27"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>153</v>
       </c>
@@ -5587,7 +5586,7 @@
       <c r="J10" s="27"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>153</v>
       </c>
@@ -5612,7 +5611,7 @@
       <c r="J11" s="27"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -5637,7 +5636,7 @@
       <c r="J12" s="27"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -5662,7 +5661,7 @@
       <c r="J13" s="27"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>153</v>
       </c>
@@ -5687,7 +5686,7 @@
       <c r="J14" s="27"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>153</v>
       </c>
@@ -5712,7 +5711,7 @@
       <c r="J15" s="27"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -5737,7 +5736,7 @@
       <c r="J16" s="27"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>153</v>
       </c>
@@ -5762,7 +5761,7 @@
       <c r="J17" s="27"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>153</v>
       </c>
@@ -5787,7 +5786,7 @@
       <c r="J18" s="27"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>153</v>
       </c>
@@ -5812,7 +5811,7 @@
       <c r="J19" s="27"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>153</v>
       </c>
@@ -5837,7 +5836,7 @@
       <c r="J20" s="27"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>153</v>
       </c>
@@ -5862,7 +5861,7 @@
       <c r="J21" s="27"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>153</v>
       </c>
@@ -5887,7 +5886,7 @@
       <c r="J22" s="27"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>153</v>
       </c>
@@ -5912,7 +5911,7 @@
       <c r="J23" s="27"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>153</v>
       </c>
@@ -5937,7 +5936,7 @@
       <c r="J24" s="27"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>153</v>
       </c>
@@ -5962,7 +5961,7 @@
       <c r="J25" s="27"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>153</v>
       </c>
@@ -5987,7 +5986,7 @@
       <c r="J26" s="27"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13">
       <c r="B27" s="1"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -5999,7 +5998,7 @@
       <c r="J27" s="27"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13">
       <c r="B28" s="1"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -6011,10 +6010,10 @@
       <c r="J28" s="27"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13">
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13">
       <c r="M30" s="1"/>
     </row>
   </sheetData>
@@ -6023,23 +6022,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA33B64-C4C0-482A-A95E-4711C4A7127B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="7" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="7" max="8" width="8.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -6074,7 +6073,7 @@
       <c r="L2" s="15"/>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -6089,7 +6088,7 @@
       <c r="J3" s="18"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13">
       <c r="A4" s="8" t="s">
         <v>172</v>
       </c>
@@ -6124,7 +6123,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="9"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="15">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -6148,7 +6147,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -6181,7 +6180,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="15">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -6207,7 +6206,7 @@
       <c r="K9" s="34"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -6233,7 +6232,7 @@
       <c r="K10" s="34"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15">
       <c r="A11" t="s">
         <v>172</v>
       </c>
@@ -6259,7 +6258,7 @@
       <c r="K11" s="34"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -6285,7 +6284,7 @@
       <c r="K12" s="34"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15">
       <c r="A13" t="s">
         <v>172</v>
       </c>
@@ -6311,7 +6310,7 @@
       <c r="K13" s="34"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15">
       <c r="A14" t="s">
         <v>172</v>
       </c>
@@ -6337,7 +6336,7 @@
       <c r="K14" s="34"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="15">
       <c r="A15" t="s">
         <v>172</v>
       </c>
@@ -6363,7 +6362,7 @@
       <c r="K15" s="34"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="15">
       <c r="A16" t="s">
         <v>172</v>
       </c>
@@ -6389,7 +6388,7 @@
       <c r="K16" s="34"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="15">
       <c r="A17" t="s">
         <v>172</v>
       </c>
@@ -6415,7 +6414,7 @@
       <c r="K17" s="34"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15">
       <c r="A18" t="s">
         <v>172</v>
       </c>
@@ -6441,7 +6440,7 @@
       <c r="K18" s="34"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="15">
       <c r="A19" t="s">
         <v>172</v>
       </c>
@@ -6467,7 +6466,7 @@
       <c r="K19" s="34"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="15">
       <c r="A20" t="s">
         <v>172</v>
       </c>
@@ -6493,7 +6492,7 @@
       <c r="K20" s="34"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="15">
       <c r="A21" t="s">
         <v>172</v>
       </c>
@@ -6519,7 +6518,7 @@
       <c r="K21" s="34"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="15">
       <c r="A22" t="s">
         <v>172</v>
       </c>
@@ -6545,7 +6544,7 @@
       <c r="K22" s="34"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="15">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -6571,7 +6570,7 @@
       <c r="K23" s="34"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15">
       <c r="A24" t="s">
         <v>172</v>
       </c>
@@ -6597,7 +6596,7 @@
       <c r="K24" s="34"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="15">
       <c r="A25" t="s">
         <v>172</v>
       </c>
@@ -6623,7 +6622,7 @@
       <c r="K25" s="34"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="15">
       <c r="A26" t="s">
         <v>172</v>
       </c>
@@ -6649,7 +6648,7 @@
       <c r="K26" s="34"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" ht="15">
       <c r="A27" t="s">
         <v>172</v>
       </c>
@@ -6675,7 +6674,7 @@
       <c r="K27" s="34"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -6701,7 +6700,7 @@
       <c r="K28" s="34"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="15">
       <c r="A29" t="s">
         <v>172</v>
       </c>
@@ -6727,7 +6726,7 @@
       <c r="K29" s="34"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="15">
       <c r="A30" t="s">
         <v>172</v>
       </c>
@@ -6753,7 +6752,7 @@
       <c r="K30" s="34"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="15">
       <c r="A31" t="s">
         <v>172</v>
       </c>
@@ -6779,7 +6778,7 @@
       <c r="K31" s="34"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="15">
       <c r="A32" t="s">
         <v>172</v>
       </c>
@@ -6805,7 +6804,7 @@
       <c r="K32" s="34"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="15">
       <c r="A33" t="s">
         <v>172</v>
       </c>
@@ -6831,7 +6830,7 @@
       <c r="K33" s="34"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="15">
       <c r="A34" t="s">
         <v>172</v>
       </c>
@@ -6857,7 +6856,7 @@
       <c r="K34" s="34"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="15">
       <c r="A35" t="s">
         <v>172</v>
       </c>
@@ -6883,7 +6882,7 @@
       <c r="K35" s="34"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" ht="15">
       <c r="A36" t="s">
         <v>172</v>
       </c>
@@ -6909,7 +6908,7 @@
       <c r="K36" s="34"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" ht="15">
       <c r="A37" t="s">
         <v>172</v>
       </c>
@@ -6935,7 +6934,7 @@
       <c r="K37" s="34"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" ht="15">
       <c r="A38" t="s">
         <v>172</v>
       </c>
@@ -6961,7 +6960,7 @@
       <c r="K38" s="34"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" ht="15">
       <c r="A39" t="s">
         <v>172</v>
       </c>
@@ -6987,7 +6986,7 @@
       <c r="K39" s="34"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" ht="15">
       <c r="A40" t="s">
         <v>172</v>
       </c>
@@ -7013,7 +7012,7 @@
       <c r="K40" s="34"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" ht="15">
       <c r="A41" t="s">
         <v>172</v>
       </c>
@@ -7039,7 +7038,7 @@
       <c r="K41" s="34"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" ht="15">
       <c r="A42" t="s">
         <v>172</v>
       </c>
@@ -7065,7 +7064,7 @@
       <c r="K42" s="34"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" ht="15">
       <c r="A43" t="s">
         <v>172</v>
       </c>
@@ -7091,7 +7090,7 @@
       <c r="K43" s="34"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" ht="15">
       <c r="A44" t="s">
         <v>172</v>
       </c>
@@ -7117,7 +7116,7 @@
       <c r="K44" s="34"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" ht="15">
       <c r="A45" t="s">
         <v>172</v>
       </c>
@@ -7143,7 +7142,7 @@
       <c r="K45" s="34"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" ht="15">
       <c r="A46" t="s">
         <v>172</v>
       </c>
@@ -7169,7 +7168,7 @@
       <c r="K46" s="34"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" ht="15">
       <c r="A47" t="s">
         <v>172</v>
       </c>
@@ -7195,7 +7194,7 @@
       <c r="K47" s="34"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" ht="15">
       <c r="A48" t="s">
         <v>172</v>
       </c>
@@ -7221,7 +7220,7 @@
       <c r="K48" s="34"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" ht="15">
       <c r="A49" t="s">
         <v>172</v>
       </c>
@@ -7255,7 +7254,7 @@
       <c r="K49" s="34"/>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" ht="15">
       <c r="A50" t="s">
         <v>172</v>
       </c>
@@ -7281,7 +7280,7 @@
       <c r="K50" s="34"/>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" ht="15">
       <c r="A51" t="s">
         <v>172</v>
       </c>
@@ -7307,7 +7306,7 @@
       <c r="K51" s="34"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" ht="15">
       <c r="A52" t="s">
         <v>172</v>
       </c>
@@ -7333,7 +7332,7 @@
       <c r="K52" s="34"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" ht="15">
       <c r="A53" t="s">
         <v>172</v>
       </c>
@@ -7359,7 +7358,7 @@
       <c r="K53" s="34"/>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" ht="15">
       <c r="A54" t="s">
         <v>172</v>
       </c>
@@ -7385,7 +7384,7 @@
       <c r="K54" s="34"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" ht="15">
       <c r="A55" t="s">
         <v>172</v>
       </c>
@@ -7411,7 +7410,7 @@
       <c r="K55" s="34"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" ht="15">
       <c r="A56" t="s">
         <v>172</v>
       </c>
@@ -7437,7 +7436,7 @@
       <c r="K56" s="34"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" ht="15">
       <c r="A57" t="s">
         <v>172</v>
       </c>
@@ -7463,7 +7462,7 @@
       <c r="K57" s="34"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" ht="15">
       <c r="A58" t="s">
         <v>172</v>
       </c>
@@ -7489,7 +7488,7 @@
       <c r="K58" s="34"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" ht="15">
       <c r="A59" t="s">
         <v>172</v>
       </c>
@@ -7515,7 +7514,7 @@
       <c r="K59" s="34"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" ht="15">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -7541,7 +7540,7 @@
       <c r="K60" s="34"/>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" ht="15">
       <c r="A61" t="s">
         <v>172</v>
       </c>
@@ -7567,7 +7566,7 @@
       <c r="K61" s="34"/>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" ht="15">
       <c r="A62" t="s">
         <v>172</v>
       </c>
@@ -7593,7 +7592,7 @@
       <c r="K62" s="34"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" ht="15">
       <c r="A63" t="s">
         <v>172</v>
       </c>
@@ -7619,7 +7618,7 @@
       <c r="K63" s="34"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" ht="15">
       <c r="A64" t="s">
         <v>172</v>
       </c>
@@ -7645,7 +7644,7 @@
       <c r="K64" s="34"/>
       <c r="L64" s="4"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" ht="15">
       <c r="A65" t="s">
         <v>172</v>
       </c>
@@ -7671,7 +7670,7 @@
       <c r="K65" s="34"/>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" ht="15">
       <c r="A66" t="s">
         <v>172</v>
       </c>
@@ -7697,7 +7696,7 @@
       <c r="K66" s="34"/>
       <c r="L66" s="4"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" ht="15">
       <c r="A67" t="s">
         <v>172</v>
       </c>
@@ -7723,22 +7722,22 @@
       <c r="K67" s="34"/>
       <c r="L67" s="4"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12">
       <c r="B68" s="32"/>
       <c r="C68" s="32"/>
       <c r="E68" s="32"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12">
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12">
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12">
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12">
       <c r="L72" s="1"/>
     </row>
   </sheetData>
@@ -7748,21 +7747,21 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E5554E-EACA-4BAA-8F69-0113BAE33AB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -7797,7 +7796,7 @@
       <c r="L2" s="15"/>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -7812,7 +7811,7 @@
       <c r="J3" s="18"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="8" t="s">
         <v>236</v>
       </c>
@@ -7847,7 +7846,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="9"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="15">
       <c r="B5" s="34"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -7858,7 +7857,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="15">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -7882,7 +7881,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -7915,7 +7914,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="15">
       <c r="A9" t="s">
         <v>236</v>
       </c>
@@ -7929,18 +7928,16 @@
       <c r="E9" s="2">
         <v>0.47866451539592519</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9" s="34">
         <v>1.37</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4">
         <v>-33.6</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" ht="15">
       <c r="A10" t="s">
         <v>236</v>
       </c>
@@ -7954,18 +7951,16 @@
       <c r="E10" s="2">
         <v>0.48698955024883572</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="G10" s="34">
         <v>1.88</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4">
+      <c r="H10" s="4"/>
+      <c r="I10" s="4">
         <v>-33.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="15">
       <c r="A11" t="s">
         <v>236</v>
       </c>
@@ -7979,18 +7974,16 @@
       <c r="E11" s="2">
         <v>0.42826142614885543</v>
       </c>
-      <c r="G11" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="G11" s="34">
         <v>0.46</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4">
+      <c r="H11" s="4"/>
+      <c r="I11" s="4">
         <v>-31.85</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" ht="15">
       <c r="A12" t="s">
         <v>236</v>
       </c>
@@ -8004,18 +7997,16 @@
       <c r="E12" s="2">
         <v>0.43784301429687189</v>
       </c>
-      <c r="G12" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H12" s="4">
+      <c r="G12" s="34">
         <v>0.12</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
         <v>-31.98</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" ht="15">
       <c r="A13" t="s">
         <v>236</v>
       </c>
@@ -8029,18 +8020,16 @@
       <c r="E13" s="2">
         <v>0.43394369794295196</v>
       </c>
-      <c r="G13" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="H13" s="4">
+      <c r="G13" s="34">
         <v>-0.63</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4">
         <v>-32.26</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" ht="15">
       <c r="A14" t="s">
         <v>236</v>
       </c>
@@ -8054,18 +8043,16 @@
       <c r="E14" s="2">
         <v>0.47928188432834978</v>
       </c>
-      <c r="G14" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="H14" s="4">
+      <c r="G14" s="34">
         <v>-0.86</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4">
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
         <v>-31.62</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" ht="15">
       <c r="A15" t="s">
         <v>236</v>
       </c>
@@ -8079,18 +8066,16 @@
       <c r="E15" s="2">
         <v>0.43506160926739967</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="G15" s="34">
         <v>-0.12</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4">
+      <c r="H15" s="4"/>
+      <c r="I15" s="4">
         <v>-34.07</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" ht="15">
       <c r="A16" t="s">
         <v>236</v>
       </c>
@@ -8104,18 +8089,16 @@
       <c r="E16" s="2">
         <v>0.44301149559071268</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="H16" s="4">
+      <c r="G16" s="34">
         <v>2.34</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4">
+      <c r="H16" s="4"/>
+      <c r="I16" s="4">
         <v>-32.61</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" ht="15">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -8129,18 +8112,16 @@
       <c r="E17" s="2">
         <v>0.44229009618027304</v>
       </c>
-      <c r="G17" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="H17" s="4">
+      <c r="G17" s="34">
         <v>-0.03</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4">
+      <c r="H17" s="4"/>
+      <c r="I17" s="4">
         <v>-35.22</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" ht="15">
       <c r="A18" t="s">
         <v>236</v>
       </c>
@@ -8154,18 +8135,16 @@
       <c r="E18" s="2">
         <v>0.46572465835029259</v>
       </c>
-      <c r="G18" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="H18" s="4">
+      <c r="G18" s="34">
         <v>2.56</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4">
+      <c r="H18" s="4"/>
+      <c r="I18" s="4">
         <v>-34.799999999999997</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" ht="15">
       <c r="A19" t="s">
         <v>236</v>
       </c>
@@ -8179,18 +8158,16 @@
       <c r="E19" s="2">
         <v>0.48742933324688958</v>
       </c>
-      <c r="G19" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="H19" s="4">
+      <c r="G19" s="34">
         <v>2.82</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4">
+      <c r="H19" s="4"/>
+      <c r="I19" s="4">
         <v>-36.94</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" ht="15">
       <c r="A20" t="s">
         <v>236</v>
       </c>
@@ -8204,18 +8181,16 @@
       <c r="E20" s="2">
         <v>0.43565853529435611</v>
       </c>
-      <c r="G20" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="H20" s="4">
+      <c r="G20" s="34">
         <v>0.66</v>
       </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4">
+      <c r="H20" s="4"/>
+      <c r="I20" s="4">
         <v>-33.200000000000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" ht="15">
       <c r="A21" t="s">
         <v>236</v>
       </c>
@@ -8229,18 +8204,16 @@
       <c r="E21" s="2">
         <v>0.41787825366868347</v>
       </c>
-      <c r="G21" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="H21" s="4">
+      <c r="G21" s="34">
         <v>1.41</v>
       </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4">
+      <c r="H21" s="4"/>
+      <c r="I21" s="4">
         <v>-33.799999999999997</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" ht="15">
       <c r="A22" t="s">
         <v>236</v>
       </c>
@@ -8254,18 +8227,16 @@
       <c r="E22" s="2">
         <v>0.4632356375118532</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="H22" s="4">
+      <c r="G22" s="34">
         <v>1.86</v>
       </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4">
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
         <v>-33.18</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" ht="15">
       <c r="A23" t="s">
         <v>236</v>
       </c>
@@ -8279,18 +8250,16 @@
       <c r="E23" s="2">
         <v>0.4812524582095935</v>
       </c>
-      <c r="G23" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="H23" s="4">
+      <c r="G23" s="34">
         <v>1.94</v>
       </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4">
+      <c r="H23" s="4"/>
+      <c r="I23" s="4">
         <v>-32.25</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" ht="15">
       <c r="A24" t="s">
         <v>236</v>
       </c>
@@ -8304,18 +8273,16 @@
       <c r="E24" s="2">
         <v>0.42735802103562331</v>
       </c>
-      <c r="G24" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="H24" s="4">
+      <c r="G24" s="34">
         <v>0.86</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4">
+      <c r="H24" s="4"/>
+      <c r="I24" s="4">
         <v>-35.61</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" ht="15">
       <c r="A25" t="s">
         <v>236</v>
       </c>
@@ -8329,18 +8296,16 @@
       <c r="E25" s="2">
         <v>0.42864062422110677</v>
       </c>
-      <c r="G25" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="H25" s="4">
+      <c r="G25" s="34">
         <v>0.67</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4">
         <v>-34.74</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" ht="15">
       <c r="A26" t="s">
         <v>236</v>
       </c>
@@ -8354,18 +8319,16 @@
       <c r="E26" s="2">
         <v>0.4625106483743614</v>
       </c>
-      <c r="G26" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="H26" s="4">
+      <c r="G26" s="34">
         <v>1.91</v>
       </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4">
+      <c r="H26" s="4"/>
+      <c r="I26" s="4">
         <v>-31.42</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" ht="15">
       <c r="A27" t="s">
         <v>236</v>
       </c>
@@ -8379,18 +8342,16 @@
       <c r="E27" s="2">
         <v>0.39563476018243021</v>
       </c>
-      <c r="G27" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="G27" s="34">
         <v>1.86</v>
       </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4">
+      <c r="H27" s="4"/>
+      <c r="I27" s="4">
         <v>-33.86</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" ht="15">
       <c r="A28" t="s">
         <v>236</v>
       </c>
@@ -8404,18 +8365,16 @@
       <c r="E28" s="2">
         <v>0.48107433198276028</v>
       </c>
-      <c r="G28" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="H28" s="4">
+      <c r="G28" s="34">
         <v>0.25</v>
       </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4">
+      <c r="H28" s="4"/>
+      <c r="I28" s="4">
         <v>-33.65</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" ht="15">
       <c r="A29" t="s">
         <v>236</v>
       </c>
@@ -8429,18 +8388,16 @@
       <c r="E29" s="2">
         <v>0.45512527237990563</v>
       </c>
-      <c r="G29" s="34" t="s">
-        <v>257</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="G29" s="34">
         <v>-1.1599999999999999</v>
       </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4">
+      <c r="H29" s="4"/>
+      <c r="I29" s="4">
         <v>-34.880000000000003</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" t="s">
         <v>236</v>
       </c>
@@ -8454,18 +8411,16 @@
       <c r="E30" s="2">
         <v>0.48928758074396705</v>
       </c>
-      <c r="G30" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="H30" s="4">
+      <c r="G30" s="34">
         <v>0.44</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4">
+      <c r="H30" s="4"/>
+      <c r="I30" s="4">
         <v>-33.24</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15">
       <c r="A31" t="s">
         <v>236</v>
       </c>
@@ -8479,18 +8434,16 @@
       <c r="E31" s="2">
         <v>0.44737747009421264</v>
       </c>
-      <c r="G31" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="H31" s="4">
+      <c r="G31" s="34">
         <v>-0.42</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4">
+      <c r="H31" s="4"/>
+      <c r="I31" s="4">
         <v>-34.64</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" t="s">
         <v>236</v>
       </c>
@@ -8504,18 +8457,16 @@
       <c r="E32" s="2">
         <v>0.39322177743596315</v>
       </c>
-      <c r="G32" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="H32" s="4">
+      <c r="G32" s="34">
         <v>-0.3</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4">
+      <c r="H32" s="4"/>
+      <c r="I32" s="4">
         <v>-31.32</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" t="s">
         <v>236</v>
       </c>
@@ -8529,18 +8480,16 @@
       <c r="E33" s="2">
         <v>0.3990582769402648</v>
       </c>
-      <c r="G33" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="H33" s="4">
+      <c r="G33" s="34">
         <v>0.5</v>
       </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4">
         <v>-34.770000000000003</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" t="s">
         <v>236</v>
       </c>
@@ -8554,18 +8503,16 @@
       <c r="E34" s="2">
         <v>0.45217282160825922</v>
       </c>
-      <c r="G34" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="H34" s="4">
+      <c r="G34" s="34">
         <v>-0.82</v>
       </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4">
+      <c r="H34" s="4"/>
+      <c r="I34" s="4">
         <v>-34.43</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15">
       <c r="A35" t="s">
         <v>236</v>
       </c>
@@ -8579,18 +8526,16 @@
       <c r="E35" s="2">
         <v>0.43963250808946686</v>
       </c>
-      <c r="G35" s="34" t="s">
-        <v>263</v>
-      </c>
-      <c r="H35" s="4">
+      <c r="G35" s="34">
         <v>-3.23</v>
       </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4">
         <v>-29.82</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15">
       <c r="A36" t="s">
         <v>236</v>
       </c>
@@ -8604,18 +8549,16 @@
       <c r="E36" s="2">
         <v>0.46367475025585508</v>
       </c>
-      <c r="G36" s="34" t="s">
-        <v>264</v>
-      </c>
-      <c r="H36" s="4">
+      <c r="G36" s="34">
         <v>-1.1599999999999999</v>
       </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4">
+      <c r="H36" s="4"/>
+      <c r="I36" s="4">
         <v>-24.93</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15">
       <c r="A37" t="s">
         <v>236</v>
       </c>
@@ -8629,18 +8572,16 @@
       <c r="E37" s="2">
         <v>0.48046196731139201</v>
       </c>
-      <c r="G37" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="H37" s="4">
+      <c r="G37" s="34">
         <v>-1.41</v>
       </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4">
         <v>-26.65</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15">
       <c r="A38" t="s">
         <v>236</v>
       </c>
@@ -8654,18 +8595,16 @@
       <c r="E38" s="2">
         <v>0.47090408010544349</v>
       </c>
-      <c r="G38" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="H38" s="4">
+      <c r="G38" s="34">
         <v>-1.08</v>
       </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4">
+      <c r="H38" s="4"/>
+      <c r="I38" s="4">
         <v>-23.43</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" ht="15">
       <c r="A39" t="s">
         <v>236</v>
       </c>
@@ -8679,19 +8618,17 @@
       <c r="E39" s="2">
         <v>0.44303889360203419</v>
       </c>
-      <c r="G39" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="H39" s="4">
+      <c r="G39" s="34">
         <v>-0.84</v>
       </c>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4">
+      <c r="H39" s="4"/>
+      <c r="I39" s="4">
         <v>-25.88</v>
       </c>
+      <c r="J39" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G35:J39">
+  <sortState ref="G35:J39">
     <sortCondition ref="G35:G39"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -8700,22 +8637,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4EB626A-E0A8-448C-BCF6-E6D35FE53566}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S104"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="7" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -8750,7 +8687,7 @@
       <c r="L2" s="15"/>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -8765,7 +8702,7 @@
       <c r="J3" s="18"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19">
       <c r="A4" s="8" t="s">
         <v>236</v>
       </c>
@@ -8800,14 +8737,14 @@
       <c r="L4" s="8"/>
       <c r="M4" s="9"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="15">
       <c r="B5" s="34"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="15">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -8831,7 +8768,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="15">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -8864,7 +8801,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="15">
       <c r="A9" t="s">
         <v>268</v>
       </c>
@@ -8890,7 +8827,7 @@
       <c r="L9" s="1"/>
       <c r="S9" s="4"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="15">
       <c r="A10" t="s">
         <v>268</v>
       </c>
@@ -8916,7 +8853,7 @@
       <c r="L10" s="1"/>
       <c r="S10" s="4"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="15">
       <c r="A11" t="s">
         <v>268</v>
       </c>
@@ -8942,7 +8879,7 @@
       <c r="L11" s="1"/>
       <c r="S11" s="4"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="15">
       <c r="A12" t="s">
         <v>268</v>
       </c>
@@ -8968,7 +8905,7 @@
       <c r="L12" s="1"/>
       <c r="S12" s="4"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="15">
       <c r="A13" t="s">
         <v>268</v>
       </c>
@@ -8994,7 +8931,7 @@
       <c r="L13" s="1"/>
       <c r="S13" s="4"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="15">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -9020,7 +8957,7 @@
       <c r="L14" s="1"/>
       <c r="S14" s="4"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="15">
       <c r="A15" t="s">
         <v>268</v>
       </c>
@@ -9046,7 +8983,7 @@
       <c r="L15" s="1"/>
       <c r="S15" s="4"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="15">
       <c r="A16" t="s">
         <v>268</v>
       </c>
@@ -9072,7 +9009,7 @@
       <c r="L16" s="1"/>
       <c r="S16" s="4"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" ht="15">
       <c r="A17" t="s">
         <v>268</v>
       </c>
@@ -9098,7 +9035,7 @@
       <c r="L17" s="1"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="15">
       <c r="A18" t="s">
         <v>268</v>
       </c>
@@ -9124,7 +9061,7 @@
       <c r="L18" s="1"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="15">
       <c r="A19" t="s">
         <v>268</v>
       </c>
@@ -9150,7 +9087,7 @@
       <c r="L19" s="1"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="15">
       <c r="A20" t="s">
         <v>268</v>
       </c>
@@ -9176,7 +9113,7 @@
       <c r="L20" s="1"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="15">
       <c r="A21" t="s">
         <v>268</v>
       </c>
@@ -9202,7 +9139,7 @@
       <c r="L21" s="1"/>
       <c r="S21" s="4"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" ht="15">
       <c r="A22" t="s">
         <v>268</v>
       </c>
@@ -9228,7 +9165,7 @@
       <c r="L22" s="1"/>
       <c r="S22" s="4"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="15">
       <c r="A23" t="s">
         <v>268</v>
       </c>
@@ -9254,7 +9191,7 @@
       <c r="L23" s="1"/>
       <c r="S23" s="4"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="15">
       <c r="A24" t="s">
         <v>268</v>
       </c>
@@ -9280,7 +9217,7 @@
       <c r="L24" s="1"/>
       <c r="S24" s="4"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" ht="15">
       <c r="A25" t="s">
         <v>268</v>
       </c>
@@ -9306,7 +9243,7 @@
       <c r="L25" s="1"/>
       <c r="S25" s="4"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" ht="15">
       <c r="A26" t="s">
         <v>268</v>
       </c>
@@ -9332,7 +9269,7 @@
       <c r="L26" s="1"/>
       <c r="S26" s="4"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" ht="15">
       <c r="A27" t="s">
         <v>268</v>
       </c>
@@ -9358,7 +9295,7 @@
       <c r="L27" s="1"/>
       <c r="S27" s="4"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" ht="15">
       <c r="A28" t="s">
         <v>268</v>
       </c>
@@ -9384,7 +9321,7 @@
       <c r="L28" s="1"/>
       <c r="S28" s="4"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" ht="15">
       <c r="A29" t="s">
         <v>268</v>
       </c>
@@ -9410,7 +9347,7 @@
       <c r="L29" s="1"/>
       <c r="S29" s="4"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" ht="15">
       <c r="A30" t="s">
         <v>268</v>
       </c>
@@ -9436,7 +9373,7 @@
       <c r="L30" s="1"/>
       <c r="S30" s="4"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" ht="15">
       <c r="A31" t="s">
         <v>268</v>
       </c>
@@ -9462,7 +9399,7 @@
       <c r="L31" s="1"/>
       <c r="S31" s="4"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" ht="15">
       <c r="A32" t="s">
         <v>268</v>
       </c>
@@ -9488,7 +9425,7 @@
       <c r="L32" s="1"/>
       <c r="S32" s="4"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" ht="15">
       <c r="A33" t="s">
         <v>268</v>
       </c>
@@ -9514,7 +9451,7 @@
       <c r="L33" s="1"/>
       <c r="S33" s="4"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" ht="15">
       <c r="A34" t="s">
         <v>268</v>
       </c>
@@ -9540,7 +9477,7 @@
       <c r="L34" s="1"/>
       <c r="S34" s="4"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" ht="15">
       <c r="A35" t="s">
         <v>268</v>
       </c>
@@ -9566,7 +9503,7 @@
       <c r="L35" s="1"/>
       <c r="S35" s="4"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" ht="15">
       <c r="A36" t="s">
         <v>268</v>
       </c>
@@ -9592,7 +9529,7 @@
       <c r="L36" s="1"/>
       <c r="S36" s="4"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" ht="15">
       <c r="A37" t="s">
         <v>268</v>
       </c>
@@ -9618,7 +9555,7 @@
       <c r="L37" s="1"/>
       <c r="S37" s="4"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" ht="15">
       <c r="A38" t="s">
         <v>268</v>
       </c>
@@ -9644,7 +9581,7 @@
       <c r="L38" s="1"/>
       <c r="S38" s="4"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" ht="15">
       <c r="A39" t="s">
         <v>268</v>
       </c>
@@ -9670,7 +9607,7 @@
       <c r="L39" s="1"/>
       <c r="S39" s="4"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" ht="15">
       <c r="A40" t="s">
         <v>268</v>
       </c>
@@ -9696,7 +9633,7 @@
       <c r="L40" s="1"/>
       <c r="S40" s="4"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" ht="15">
       <c r="A41" t="s">
         <v>268</v>
       </c>
@@ -9722,7 +9659,7 @@
       <c r="L41" s="1"/>
       <c r="S41" s="4"/>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" ht="15">
       <c r="A42" t="s">
         <v>268</v>
       </c>
@@ -9748,7 +9685,7 @@
       <c r="L42" s="1"/>
       <c r="S42" s="4"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" ht="15">
       <c r="A43" t="s">
         <v>268</v>
       </c>
@@ -9774,7 +9711,7 @@
       <c r="L43" s="1"/>
       <c r="S43" s="4"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" ht="15">
       <c r="A44" t="s">
         <v>268</v>
       </c>
@@ -9800,7 +9737,7 @@
       <c r="L44" s="1"/>
       <c r="S44" s="4"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" ht="15">
       <c r="A45" t="s">
         <v>268</v>
       </c>
@@ -9826,7 +9763,7 @@
       <c r="L45" s="1"/>
       <c r="S45" s="4"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" ht="15">
       <c r="A46" t="s">
         <v>268</v>
       </c>
@@ -9852,7 +9789,7 @@
       <c r="L46" s="1"/>
       <c r="S46" s="4"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" ht="15">
       <c r="A47" t="s">
         <v>268</v>
       </c>
@@ -9878,7 +9815,7 @@
       <c r="L47" s="1"/>
       <c r="S47" s="4"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" ht="15">
       <c r="A48" t="s">
         <v>268</v>
       </c>
@@ -9904,7 +9841,7 @@
       <c r="L48" s="1"/>
       <c r="S48" s="4"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" ht="15">
       <c r="A49" t="s">
         <v>268</v>
       </c>
@@ -9930,7 +9867,7 @@
       <c r="L49" s="1"/>
       <c r="S49" s="4"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" ht="15">
       <c r="A50" t="s">
         <v>268</v>
       </c>
@@ -9956,7 +9893,7 @@
       <c r="L50" s="1"/>
       <c r="S50" s="4"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" ht="15">
       <c r="A51" t="s">
         <v>268</v>
       </c>
@@ -9982,7 +9919,7 @@
       <c r="L51" s="1"/>
       <c r="S51" s="4"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" ht="15">
       <c r="A52" t="s">
         <v>268</v>
       </c>
@@ -10008,7 +9945,7 @@
       <c r="L52" s="1"/>
       <c r="S52" s="4"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" ht="15">
       <c r="A53" t="s">
         <v>268</v>
       </c>
@@ -10034,7 +9971,7 @@
       <c r="L53" s="1"/>
       <c r="S53" s="4"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" ht="15">
       <c r="A54" t="s">
         <v>268</v>
       </c>
@@ -10060,7 +9997,7 @@
       <c r="L54" s="1"/>
       <c r="S54" s="4"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" ht="15">
       <c r="A55" t="s">
         <v>268</v>
       </c>
@@ -10086,7 +10023,7 @@
       <c r="L55" s="1"/>
       <c r="S55" s="4"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" ht="15">
       <c r="A56" t="s">
         <v>268</v>
       </c>
@@ -10112,7 +10049,7 @@
       <c r="L56" s="1"/>
       <c r="S56" s="4"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" ht="15">
       <c r="A57" t="s">
         <v>268</v>
       </c>
@@ -10138,7 +10075,7 @@
       <c r="L57" s="1"/>
       <c r="S57" s="4"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" ht="15">
       <c r="A58" t="s">
         <v>268</v>
       </c>
@@ -10164,7 +10101,7 @@
       <c r="L58" s="1"/>
       <c r="S58" s="4"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" ht="15">
       <c r="A59" t="s">
         <v>268</v>
       </c>
@@ -10190,7 +10127,7 @@
       <c r="L59" s="1"/>
       <c r="S59" s="4"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" ht="15">
       <c r="A60" t="s">
         <v>268</v>
       </c>
@@ -10216,7 +10153,7 @@
       <c r="L60" s="1"/>
       <c r="S60" s="4"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" ht="15">
       <c r="A61" t="s">
         <v>268</v>
       </c>
@@ -10242,7 +10179,7 @@
       <c r="L61" s="1"/>
       <c r="S61" s="4"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" ht="15">
       <c r="A62" t="s">
         <v>268</v>
       </c>
@@ -10268,7 +10205,7 @@
       <c r="L62" s="1"/>
       <c r="S62" s="4"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" ht="15">
       <c r="A63" t="s">
         <v>268</v>
       </c>
@@ -10294,7 +10231,7 @@
       <c r="L63" s="1"/>
       <c r="S63" s="4"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" ht="15">
       <c r="A64" t="s">
         <v>268</v>
       </c>
@@ -10320,7 +10257,7 @@
       <c r="L64" s="1"/>
       <c r="S64" s="4"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19" ht="15">
       <c r="A65" t="s">
         <v>268</v>
       </c>
@@ -10346,7 +10283,7 @@
       <c r="L65" s="1"/>
       <c r="S65" s="4"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19" ht="15">
       <c r="A66" t="s">
         <v>268</v>
       </c>
@@ -10372,7 +10309,7 @@
       <c r="L66" s="1"/>
       <c r="S66" s="4"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" ht="15">
       <c r="A67" t="s">
         <v>268</v>
       </c>
@@ -10398,7 +10335,7 @@
       <c r="L67" s="1"/>
       <c r="S67" s="4"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19" ht="15">
       <c r="A68" t="s">
         <v>268</v>
       </c>
@@ -10424,7 +10361,7 @@
       <c r="L68" s="1"/>
       <c r="S68" s="4"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19" ht="15">
       <c r="A69" t="s">
         <v>268</v>
       </c>
@@ -10450,7 +10387,7 @@
       <c r="L69" s="1"/>
       <c r="S69" s="4"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19" ht="15">
       <c r="A70" t="s">
         <v>268</v>
       </c>
@@ -10476,7 +10413,7 @@
       <c r="L70" s="1"/>
       <c r="S70" s="4"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19" ht="15">
       <c r="A71" t="s">
         <v>268</v>
       </c>
@@ -10502,7 +10439,7 @@
       <c r="L71" s="1"/>
       <c r="S71" s="4"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19" ht="15">
       <c r="A72" t="s">
         <v>268</v>
       </c>
@@ -10528,7 +10465,7 @@
       <c r="L72" s="1"/>
       <c r="S72" s="4"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19" ht="15">
       <c r="A73" t="s">
         <v>268</v>
       </c>
@@ -10554,7 +10491,7 @@
       <c r="L73" s="1"/>
       <c r="S73" s="4"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19" ht="15">
       <c r="A74" t="s">
         <v>268</v>
       </c>
@@ -10580,7 +10517,7 @@
       <c r="L74" s="1"/>
       <c r="S74" s="4"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19" ht="15">
       <c r="A75" t="s">
         <v>268</v>
       </c>
@@ -10606,7 +10543,7 @@
       <c r="L75" s="1"/>
       <c r="S75" s="4"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19" ht="15">
       <c r="A76" t="s">
         <v>268</v>
       </c>
@@ -10632,7 +10569,7 @@
       <c r="L76" s="1"/>
       <c r="S76" s="4"/>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19" ht="15">
       <c r="A77" t="s">
         <v>268</v>
       </c>
@@ -10658,7 +10595,7 @@
       <c r="L77" s="1"/>
       <c r="S77" s="4"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19" ht="15">
       <c r="A78" t="s">
         <v>268</v>
       </c>
@@ -10684,7 +10621,7 @@
       <c r="L78" s="1"/>
       <c r="S78" s="4"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19" ht="15">
       <c r="A79" t="s">
         <v>268</v>
       </c>
@@ -10710,7 +10647,7 @@
       <c r="L79" s="1"/>
       <c r="S79" s="4"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19" ht="15">
       <c r="A80" t="s">
         <v>268</v>
       </c>
@@ -10736,7 +10673,7 @@
       <c r="L80" s="1"/>
       <c r="S80" s="4"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19" ht="15">
       <c r="A81" t="s">
         <v>268</v>
       </c>
@@ -10762,7 +10699,7 @@
       <c r="L81" s="1"/>
       <c r="S81" s="4"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19" ht="15">
       <c r="A82" t="s">
         <v>268</v>
       </c>
@@ -10788,7 +10725,7 @@
       <c r="L82" s="1"/>
       <c r="S82" s="4"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19" ht="15">
       <c r="A83" t="s">
         <v>268</v>
       </c>
@@ -10814,7 +10751,7 @@
       <c r="L83" s="1"/>
       <c r="S83" s="4"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19" ht="15">
       <c r="A84" t="s">
         <v>268</v>
       </c>
@@ -10840,7 +10777,7 @@
       <c r="L84" s="1"/>
       <c r="S84" s="4"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19" ht="15">
       <c r="A85" t="s">
         <v>268</v>
       </c>
@@ -10866,7 +10803,7 @@
       <c r="L85" s="1"/>
       <c r="S85" s="4"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19" ht="15">
       <c r="A86" t="s">
         <v>268</v>
       </c>
@@ -10892,7 +10829,7 @@
       <c r="L86" s="1"/>
       <c r="S86" s="4"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19" ht="15">
       <c r="A87" t="s">
         <v>268</v>
       </c>
@@ -10918,7 +10855,7 @@
       <c r="L87" s="1"/>
       <c r="S87" s="4"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19" ht="15">
       <c r="A88" t="s">
         <v>268</v>
       </c>
@@ -10944,7 +10881,7 @@
       <c r="L88" s="1"/>
       <c r="S88" s="4"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19" ht="15">
       <c r="A89" t="s">
         <v>268</v>
       </c>
@@ -10970,7 +10907,7 @@
       <c r="L89" s="1"/>
       <c r="S89" s="4"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19" ht="15">
       <c r="A90" t="s">
         <v>268</v>
       </c>
@@ -10996,7 +10933,7 @@
       <c r="L90" s="1"/>
       <c r="S90" s="4"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19" ht="15">
       <c r="A91" t="s">
         <v>268</v>
       </c>
@@ -11022,7 +10959,7 @@
       <c r="L91" s="1"/>
       <c r="S91" s="4"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" ht="15">
       <c r="A92" t="s">
         <v>268</v>
       </c>
@@ -11048,7 +10985,7 @@
       <c r="L92" s="1"/>
       <c r="S92" s="4"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19" ht="15">
       <c r="A93" t="s">
         <v>268</v>
       </c>
@@ -11074,7 +11011,7 @@
       <c r="L93" s="1"/>
       <c r="S93" s="4"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19" ht="15">
       <c r="A94" t="s">
         <v>268</v>
       </c>
@@ -11100,7 +11037,7 @@
       <c r="L94" s="1"/>
       <c r="S94" s="4"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19" ht="15">
       <c r="A95" t="s">
         <v>268</v>
       </c>
@@ -11126,7 +11063,7 @@
       <c r="L95" s="1"/>
       <c r="S95" s="4"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19" ht="15">
       <c r="A96" t="s">
         <v>268</v>
       </c>
@@ -11152,7 +11089,7 @@
       <c r="L96" s="1"/>
       <c r="S96" s="4"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" ht="15">
       <c r="A97" t="s">
         <v>268</v>
       </c>
@@ -11178,7 +11115,7 @@
       <c r="L97" s="1"/>
       <c r="S97" s="4"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19" ht="15">
       <c r="A98" t="s">
         <v>268</v>
       </c>
@@ -11204,37 +11141,37 @@
       <c r="L98" s="1"/>
       <c r="S98" s="4"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" ht="15">
       <c r="B99" s="1"/>
       <c r="K99" s="34"/>
       <c r="L99" s="1"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" ht="15">
       <c r="K100" s="34"/>
       <c r="L100" s="1"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" ht="15">
       <c r="B101" s="1"/>
       <c r="K101" s="34"/>
       <c r="L101" s="1"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" ht="15">
       <c r="B102" s="1"/>
       <c r="K102" s="34"/>
       <c r="L102" s="1"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" ht="15">
       <c r="B103" s="1"/>
       <c r="K103" s="34"/>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19" ht="15">
       <c r="B104" s="1"/>
       <c r="K104" s="34"/>
       <c r="L104" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K9:S98">
+  <sortState ref="K9:S98">
     <sortCondition ref="K9:K98"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -11243,20 +11180,20 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3DF3F1B-0BCA-461F-83AD-A0B9CE20019F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M64"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -11291,7 +11228,7 @@
       <c r="L2" s="15"/>
       <c r="M2" s="23"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="17"/>
       <c r="B3" s="26" t="s">
         <v>3</v>
@@ -11306,7 +11243,7 @@
       <c r="J3" s="18"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>312</v>
       </c>
@@ -11341,7 +11278,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="9"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="B5" s="35"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -11352,7 +11289,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="15">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -11376,7 +11313,7 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -11409,7 +11346,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>312</v>
       </c>
@@ -11433,7 +11370,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>312</v>
       </c>
@@ -11457,7 +11394,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>312</v>
       </c>
@@ -11481,7 +11418,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>312</v>
       </c>
@@ -11505,7 +11442,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>312</v>
       </c>
@@ -11529,7 +11466,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>312</v>
       </c>
@@ -11553,7 +11490,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>312</v>
       </c>
@@ -11577,7 +11514,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>312</v>
       </c>
@@ -11601,7 +11538,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>312</v>
       </c>
@@ -11625,7 +11562,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>312</v>
       </c>
@@ -11649,7 +11586,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>312</v>
       </c>
@@ -11673,7 +11610,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>312</v>
       </c>
@@ -11697,7 +11634,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>312</v>
       </c>
@@ -11721,7 +11658,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>312</v>
       </c>
@@ -11745,7 +11682,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>312</v>
       </c>
@@ -11769,7 +11706,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>312</v>
       </c>
@@ -11793,7 +11730,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>312</v>
       </c>
@@ -11817,7 +11754,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>312</v>
       </c>
@@ -11841,7 +11778,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>312</v>
       </c>
@@ -11865,7 +11802,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>312</v>
       </c>
@@ -11889,7 +11826,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>312</v>
       </c>
@@ -11913,7 +11850,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>312</v>
       </c>
@@ -11937,7 +11874,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>312</v>
       </c>
@@ -11961,7 +11898,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>312</v>
       </c>
@@ -11985,7 +11922,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>312</v>
       </c>
@@ -12009,7 +11946,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>312</v>
       </c>
@@ -12033,7 +11970,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>312</v>
       </c>
@@ -12057,7 +11994,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>312</v>
       </c>
@@ -12081,7 +12018,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>312</v>
       </c>
@@ -12105,7 +12042,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>312</v>
       </c>
@@ -12129,7 +12066,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>312</v>
       </c>
@@ -12153,7 +12090,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>312</v>
       </c>
@@ -12177,7 +12114,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>312</v>
       </c>
@@ -12201,7 +12138,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>312</v>
       </c>
@@ -12225,7 +12162,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>312</v>
       </c>
@@ -12249,7 +12186,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>312</v>
       </c>
@@ -12273,7 +12210,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>312</v>
       </c>
@@ -12297,7 +12234,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>312</v>
       </c>
@@ -12321,7 +12258,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>312</v>
       </c>
@@ -12345,7 +12282,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>312</v>
       </c>
@@ -12369,7 +12306,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>312</v>
       </c>
@@ -12393,7 +12330,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>312</v>
       </c>
@@ -12417,7 +12354,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>312</v>
       </c>
@@ -12441,7 +12378,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>312</v>
       </c>
@@ -12465,7 +12402,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>312</v>
       </c>
@@ -12489,7 +12426,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>312</v>
       </c>
@@ -12513,7 +12450,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>312</v>
       </c>
@@ -12537,7 +12474,7 @@
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>312</v>
       </c>
@@ -12561,7 +12498,7 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>312</v>
       </c>
@@ -12585,7 +12522,7 @@
       </c>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>312</v>
       </c>
@@ -12609,7 +12546,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>312</v>
       </c>
@@ -12633,7 +12570,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>312</v>
       </c>
@@ -12657,7 +12594,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>312</v>
       </c>
@@ -12681,7 +12618,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10">
       <c r="B62" s="35"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
@@ -12692,7 +12629,7 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10">
       <c r="B63" s="35"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
@@ -12703,7 +12640,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10">
       <c r="B64" s="35"/>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
@@ -12956,15 +12893,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ada196f1-b314-4482-a04c-235b25854a0d" xsi:nil="true"/>
@@ -12973,6 +12901,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12995,14 +12932,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5D22202-BD69-427B-8F3C-87B78C5BC58C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D84CB959-57D3-4B39-99DC-7C9003601385}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -13017,4 +12946,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5D22202-BD69-427B-8F3C-87B78C5BC58C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>